--- a/graficos/LDA_mejores_porc.xlsx
+++ b/graficos/LDA_mejores_porc.xlsx
@@ -73,55 +73,55 @@
     <t>comisión_lim_dictamen_dom_K3_-</t>
   </si>
   <si>
+    <t>orps</t>
+  </si>
+  <si>
+    <t>orps_dictamen_dom_K3_-</t>
+  </si>
+  <si>
     <t>comisión</t>
   </si>
   <si>
     <t>comisión_dictamen_dom_K3_-</t>
   </si>
   <si>
-    <t>orps</t>
-  </si>
-  <si>
-    <t>orps_dictamen_dom_K3_-</t>
-  </si>
-  <si>
     <t>orps_lim_dictamen_dom_K4_-</t>
   </si>
   <si>
     <t>todos_dictamen_dom_K5_-</t>
   </si>
   <si>
+    <t>orps_dictamen_dom_K4_-</t>
+  </si>
+  <si>
     <t>comisión_dictamen_dom_K4_-</t>
   </si>
   <si>
-    <t>orps_dictamen_dom_K4_-</t>
-  </si>
-  <si>
     <t>todos_dictamen_dom_K6_-</t>
   </si>
   <si>
-    <t>denuncia_dom</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_dom_K3_-</t>
+    <t>antecedentes_dom</t>
+  </si>
+  <si>
+    <t>orps_lim_antecedentes_dom_K3_-</t>
   </si>
   <si>
     <t>orps_lim_dictamen_dom_K5_-</t>
   </si>
   <si>
-    <t>orps_denuncia_dom_K3_-</t>
-  </si>
-  <si>
-    <t>comisión_denuncia_dom_K3_-</t>
+    <t>comisión_antecedentes_dom_K3_-</t>
+  </si>
+  <si>
+    <t>orps_antecedentes_dom_K3_-</t>
+  </si>
+  <si>
+    <t>comisión_dictamen_dom_K5_-</t>
   </si>
   <si>
     <t>orps_dictamen_dom_K5_-</t>
   </si>
   <si>
-    <t>comisión_dictamen_dom_K5_-</t>
-  </si>
-  <si>
-    <t>orps_lim_denuncia_dom_K4_-</t>
+    <t>orps_lim_antecedentes_dom_K4_-</t>
   </si>
   <si>
     <t>todos_dictamen_dom_K7_-</t>
